--- a/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra95ede7574614468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R342a9dcd807a45b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R269aaad8c612471a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra6b59be6d66f4562"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cb6cd17f8eb4110"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c791c0dada949b5"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R342a9dcd807a45b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4fb2af14430a4e10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra6b59be6d66f4562"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a192917cf2e442c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c791c0dada949b5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde693805246e4f47"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4fb2af14430a4e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R091516faf1f5428a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a192917cf2e442c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R622a78ca57e344b8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde693805246e4f47"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1381760989834f3e"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R091516faf1f5428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d18dd5a90c04898"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R622a78ca57e344b8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd3f5136b5938414c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1381760989834f3e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd172c23da3144e30"/>
 </x:worksheet>
 </file>